--- a/exports/PIIND_full_report.xlsx
+++ b/exports/PIIND_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>3.71</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44578.55208333334</v>
+        <v>44579.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2794</v>
+        <v>2751.9</v>
       </c>
       <c r="I2" t="n">
         <v>2787.875</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.5</v>
+        <v>-4.95</v>
       </c>
       <c r="L2" t="n">
-        <v>4.15</v>
+        <v>5.14</v>
       </c>
       <c r="M2" t="n">
         <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>2.02</v>
+        <v>2.87</v>
       </c>
       <c r="O2" t="n">
         <v>-2.02</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.06</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44596.38541666666</v>
+        <v>44596.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>2505</v>
+        <v>2553</v>
       </c>
       <c r="I3" t="n">
         <v>2544.973473245536</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>8.970000000000001</v>
+        <v>7.23</v>
       </c>
       <c r="L3" t="n">
         <v>2.29</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.93</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2495.05</v>
+        <v>2445</v>
       </c>
       <c r="I4" t="n">
         <v>2473.336241077258</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.27</v>
+        <v>-4.23</v>
       </c>
       <c r="L4" t="n">
-        <v>3.31</v>
+        <v>6.36</v>
       </c>
       <c r="M4" t="n">
         <v>3.06</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.8</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44631.38541666666</v>
+        <v>44631.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>2567</v>
+        <v>2587.4</v>
       </c>
       <c r="I5" t="n">
         <v>2573.19148366073</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.99</v>
+        <v>-5.82</v>
       </c>
       <c r="L5" t="n">
         <v>6.27</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.29</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>2821</v>
+        <v>2805</v>
       </c>
       <c r="I6" t="n">
         <v>2817.271434657704</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K6" t="n">
-        <v>9.029999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="L6" t="n">
         <v>1.62</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.33</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44699.38541666666</v>
+        <v>44699.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>2608</v>
+        <v>2630</v>
       </c>
       <c r="I7" t="n">
         <v>2629.734049088284</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>7.02</v>
+        <v>6.24</v>
       </c>
       <c r="L7" t="n">
         <v>0.95</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44726.38541666666</v>
+        <v>44726.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>2578.55</v>
+        <v>2538.35</v>
       </c>
       <c r="I8" t="n">
         <v>2564.387853335104</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.96</v>
+        <v>-3.48</v>
       </c>
       <c r="L8" t="n">
         <v>4.18</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.46</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44740.38541666666</v>
+        <v>44740.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>2598.6</v>
+        <v>2632.1</v>
       </c>
       <c r="I9" t="n">
         <v>2628.181095516828</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.37</v>
+        <v>-3.69</v>
       </c>
       <c r="L9" t="n">
         <v>4.32</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.32</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44809.55208333334</v>
+        <v>44810.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>3335</v>
+        <v>3272.85</v>
       </c>
       <c r="I10" t="n">
         <v>3279.035553660574</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>69</v>
+        <v>69.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>26.7</v>
+        <v>24.34</v>
       </c>
       <c r="L10" t="n">
         <v>4.56</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.31</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44852.55208333334</v>
+        <v>44853.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3090</v>
+        <v>3158.75</v>
       </c>
       <c r="I11" t="n">
         <v>3132.853051309532</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K11" t="n">
-        <v>5.59</v>
+        <v>3.49</v>
       </c>
       <c r="L11" t="n">
         <v>2.89</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.71</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3500</v>
+        <v>3394.1</v>
       </c>
       <c r="I12" t="n">
         <v>3399.447474161313</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>10.8</v>
+        <v>7.45</v>
       </c>
       <c r="L12" t="n">
         <v>2.54</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>11.02</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44908.55208333334</v>
+        <v>44909.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3480.3</v>
+        <v>3550</v>
       </c>
       <c r="I13" t="n">
         <v>3535.962896341566</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.54</v>
+        <v>-4.59</v>
       </c>
       <c r="L13" t="n">
-        <v>4.89</v>
+        <v>6.95</v>
       </c>
       <c r="M13" t="n">
         <v>1.46</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>4.9</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44929.55208333334</v>
+        <v>44930.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3417.8</v>
+        <v>3371</v>
       </c>
       <c r="I14" t="n">
         <v>3389.652994455262</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.72</v>
+        <v>-5.04</v>
       </c>
       <c r="L14" t="n">
-        <v>4.36</v>
+        <v>5.35</v>
       </c>
       <c r="M14" t="n">
         <v>0.71</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>2.42</v>
       </c>
       <c r="O14" t="n">
         <v>1.78</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.23</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44964.55208333334</v>
+        <v>44965.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3051</v>
+        <v>3155.4</v>
       </c>
       <c r="I15" t="n">
         <v>3077.816524806773</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K15" t="n">
-        <v>9.49</v>
+        <v>6.4</v>
       </c>
       <c r="L15" t="n">
         <v>2.17</v>
@@ -1296,7 +1475,7 @@
         <v>1.65</v>
       </c>
       <c r="N15" t="n">
-        <v>2.01</v>
+        <v>3.81</v>
       </c>
       <c r="O15" t="n">
         <v>-2.42</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>7.15</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3115</v>
+        <v>3039.25</v>
       </c>
       <c r="I16" t="n">
         <v>3099.585481093039</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.28</v>
+        <v>-3.68</v>
       </c>
       <c r="L16" t="n">
         <v>4.45</v>
       </c>
       <c r="M16" t="n">
-        <v>0.41</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
         <v>2.52</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.06</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45022.55208333334</v>
+        <v>45026.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>3034.85</v>
+        <v>3055</v>
       </c>
       <c r="I17" t="n">
         <v>3041.825775500358</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>0.14</v>
+        <v>-0.52</v>
       </c>
       <c r="L17" t="n">
         <v>4.3</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>5.16</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45041.55208333334</v>
+        <v>45042.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3095.45</v>
+        <v>3059.45</v>
       </c>
       <c r="I18" t="n">
         <v>3063.597797007284</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>1.32</v>
+        <v>0.15</v>
       </c>
       <c r="L18" t="n">
         <v>1.89</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="N18" t="n">
         <v>2.58</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>5.29</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>3060.05</v>
+        <v>3350</v>
       </c>
       <c r="I19" t="n">
         <v>3185.933157485652</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.02</v>
+        <v>-9.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.91</v>
+        <v>11.51</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2</v>
+        <v>5.88</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>10.32</v>
       </c>
       <c r="O19" t="n">
         <v>-0.96</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.24</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>3318.75</v>
+        <v>3275</v>
       </c>
       <c r="I20" t="n">
         <v>3311.227650787566</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.93</v>
+        <v>-2.24</v>
       </c>
       <c r="L20" t="n">
         <v>3.28</v>
@@ -1581,7 +1820,7 @@
         <v>0.18</v>
       </c>
       <c r="N20" t="n">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
         <v>10.32</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>5.02</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45069.55208333334</v>
+        <v>45070.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>3377.45</v>
+        <v>3395.95</v>
       </c>
       <c r="I21" t="n">
         <v>3391.646035639803</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.13</v>
+        <v>-3.69</v>
       </c>
       <c r="L21" t="n">
-        <v>4.1</v>
+        <v>4.58</v>
       </c>
       <c r="M21" t="n">
         <v>0.63</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.74</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45113.55208333334</v>
+        <v>45114.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3860</v>
+        <v>3746.9</v>
       </c>
       <c r="I22" t="n">
         <v>3758.329788131546</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K22" t="n">
-        <v>13.66</v>
+        <v>10.33</v>
       </c>
       <c r="L22" t="n">
         <v>1.21</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.73</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>3691.3</v>
+        <v>3781.85</v>
       </c>
       <c r="I23" t="n">
         <v>3716.409608441209</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K23" t="n">
-        <v>1.48</v>
+        <v>-0.93</v>
       </c>
       <c r="L23" t="n">
         <v>2.86</v>
       </c>
       <c r="M23" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>1.76</v>
+        <v>2.54</v>
       </c>
       <c r="O23" t="n">
         <v>-2.36</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.67</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45159.55208333334</v>
+        <v>45160.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3726.3</v>
+        <v>3699.9</v>
       </c>
       <c r="I24" t="n">
         <v>3709.814688175639</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.47</v>
+        <v>-2.17</v>
       </c>
       <c r="L24" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="M24" t="n">
         <v>0.35</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.04</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>3464.85</v>
+        <v>3504.9</v>
       </c>
       <c r="I25" t="n">
         <v>3502.274020285166</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K25" t="n">
-        <v>6.35</v>
+        <v>5.27</v>
       </c>
       <c r="L25" t="n">
         <v>1.76</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>3.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>3442.1</v>
+        <v>3408</v>
       </c>
       <c r="I26" t="n">
         <v>3417.441319655867</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.79</v>
+        <v>-2.76</v>
       </c>
       <c r="L26" t="n">
-        <v>2.11</v>
+        <v>3.23</v>
       </c>
       <c r="M26" t="n">
         <v>0.43</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>4.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3405.55</v>
+        <v>3472.95</v>
       </c>
       <c r="I27" t="n">
         <v>3434.904550746271</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.91</v>
       </c>
       <c r="L27" t="n">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="M27" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="N27" t="n">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="O27" t="n">
         <v>-1.67</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45272.38541666666</v>
+        <v>45272.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>3788.25</v>
+        <v>3484</v>
       </c>
       <c r="I28" t="n">
         <v>3729.42590299505</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>9.08</v>
+        <v>0.32</v>
       </c>
       <c r="L28" t="n">
         <v>2.64</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.29</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45322.55208333334</v>
+        <v>45323.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3376.1</v>
+        <v>3401.25</v>
       </c>
       <c r="I29" t="n">
         <v>3380.273766505997</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>50</v>
+        <v>50.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="L29" t="n">
         <v>8.76</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.01</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45404.55208333334</v>
+        <v>45405.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>3710</v>
+        <v>3688.5</v>
       </c>
       <c r="I30" t="n">
         <v>3704.70803132743</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>81.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K30" t="n">
-        <v>9.08</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>4.04</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.99</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3600</v>
+        <v>3710.65</v>
       </c>
       <c r="I31" t="n">
         <v>3680.750549711737</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K31" t="n">
-        <v>2.4</v>
+        <v>-0.6</v>
       </c>
       <c r="L31" t="n">
         <v>4.17</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.96</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45572.38541666666</v>
+        <v>45572.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>4508.75</v>
+        <v>4495</v>
       </c>
       <c r="I32" t="n">
         <v>4503.236349783673</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>138</v>
+        <v>138.1666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>21.51</v>
+        <v>21.14</v>
       </c>
       <c r="L32" t="n">
         <v>7.27</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>189</v>
+        <v>190</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.4</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>4540</v>
+        <v>4590.05</v>
       </c>
       <c r="I33" t="n">
         <v>4570.076224163063</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-1</v>
+        <v>-2.11</v>
       </c>
       <c r="L33" t="n">
         <v>3.62</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>5.49</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>4526.55</v>
+        <v>4428.5</v>
       </c>
       <c r="I34" t="n">
         <v>4439.373037454257</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.38</v>
+        <v>-3.52</v>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>3.89</v>
       </c>
       <c r="M34" t="n">
         <v>-0</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.35</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>3499.1</v>
+        <v>3621.3</v>
       </c>
       <c r="I35" t="n">
         <v>3565.371733316546</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>80.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K35" t="n">
-        <v>20.99</v>
+        <v>18.23</v>
       </c>
       <c r="L35" t="n">
         <v>2.82</v>
@@ -2436,7 +2855,7 @@
         <v>1.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.66</v>
+        <v>3.74</v>
       </c>
       <c r="O35" t="n">
         <v>-0.8100000000000001</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.73</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>3525</v>
+        <v>3394.65</v>
       </c>
       <c r="I36" t="n">
         <v>3435.246990655161</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.66</v>
+        <v>-6.26</v>
       </c>
       <c r="L36" t="n">
-        <v>4.7</v>
+        <v>6.46</v>
       </c>
       <c r="M36" t="n">
         <v>3.04</v>
       </c>
       <c r="N36" t="n">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="O36" t="n">
         <v>3.74</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.93</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3150</v>
+        <v>3226.1</v>
       </c>
       <c r="I37" t="n">
         <v>3158.454961681625</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K37" t="n">
-        <v>7.21</v>
+        <v>4.97</v>
       </c>
       <c r="L37" t="n">
         <v>3.1</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>6.82</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>3325.95</v>
+        <v>3245.65</v>
       </c>
       <c r="I38" t="n">
         <v>3315.296799959947</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K38" t="n">
-        <v>3.1</v>
+        <v>0.61</v>
       </c>
       <c r="L38" t="n">
         <v>5.62</v>
       </c>
       <c r="M38" t="n">
-        <v>1.73</v>
+        <v>8</v>
       </c>
       <c r="N38" t="n">
         <v>3.6</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.58</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>3282.35</v>
+        <v>3587.95</v>
       </c>
       <c r="I39" t="n">
         <v>3426.705641307962</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.13</v>
+        <v>-10.55</v>
       </c>
       <c r="L39" t="n">
-        <v>2.08</v>
+        <v>10.67</v>
       </c>
       <c r="M39" t="n">
-        <v>0.14</v>
+        <v>4.19</v>
       </c>
       <c r="N39" t="n">
-        <v>0.99</v>
+        <v>10.25</v>
       </c>
       <c r="O39" t="n">
         <v>-2.13</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.4</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45847.55208333334</v>
+        <v>45848.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>4169</v>
+        <v>4052.7</v>
       </c>
       <c r="I40" t="n">
         <v>4073.256330118563</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>89.16666666666667</v>
+        <v>90</v>
       </c>
       <c r="K40" t="n">
-        <v>16.19</v>
+        <v>12.95</v>
       </c>
       <c r="L40" t="n">
         <v>4.68</v>
@@ -2721,7 +3200,7 @@
         <v>2.17</v>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>3.01</v>
       </c>
       <c r="O40" t="n">
         <v>10.25</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>5.85</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45866.55208333334</v>
+        <v>45867.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>4086.4</v>
+        <v>4221.4</v>
       </c>
       <c r="I41" t="n">
         <v>4185.771058995062</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.83</v>
+        <v>-4.16</v>
       </c>
       <c r="L41" t="n">
-        <v>3.57</v>
+        <v>4.58</v>
       </c>
       <c r="M41" t="n">
         <v>0.54</v>
       </c>
       <c r="N41" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
         <v>-3.01</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.21</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45870.55208333334</v>
+        <v>45873.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>4152.3</v>
+        <v>4087</v>
       </c>
       <c r="I42" t="n">
         <v>4116.375151990208</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.64</v>
+        <v>-3.18</v>
       </c>
       <c r="L42" t="n">
         <v>4.3</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.06</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45961.55208333334</v>
+        <v>45964.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>3578.5</v>
+        <v>3693.6</v>
       </c>
       <c r="I43" t="n">
         <v>3656.927585566531</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K43" t="n">
-        <v>12.44</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L43" t="n">
         <v>2.52</v>
@@ -2892,7 +3407,7 @@
         <v>0.91</v>
       </c>
       <c r="N43" t="n">
-        <v>2.73</v>
+        <v>3.26</v>
       </c>
       <c r="O43" t="n">
         <v>-0.34</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.1</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>3772.1</v>
+        <v>3616.6</v>
       </c>
       <c r="I44" t="n">
         <v>3653.120421465066</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K44" t="n">
-        <v>2.13</v>
+        <v>-2.08</v>
       </c>
       <c r="L44" t="n">
         <v>3.44</v>
       </c>
       <c r="M44" t="n">
-        <v>0.33</v>
+        <v>0.59</v>
       </c>
       <c r="N44" t="n">
-        <v>1.1</v>
+        <v>5.09</v>
       </c>
       <c r="O44" t="n">
         <v>3.26</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46063.55208333334</v>
+        <v>46064.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>3171</v>
+        <v>3284.8</v>
       </c>
       <c r="I45" t="n">
         <v>3264.00006576653</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>90.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K45" t="n">
-        <v>12.32</v>
+        <v>9.17</v>
       </c>
       <c r="L45" t="n">
         <v>3.69</v>
@@ -3006,7 +3545,7 @@
         <v>4.06</v>
       </c>
       <c r="N45" t="n">
-        <v>2.72</v>
+        <v>3.37</v>
       </c>
       <c r="O45" t="n">
         <v>-5.09</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46066.55208333334</v>
+        <v>46069.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>3167.8</v>
+        <v>3040.6</v>
       </c>
       <c r="I46" t="n">
         <v>3053.938793445592</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.56</v>
+        <v>-7.43</v>
       </c>
       <c r="L46" t="n">
-        <v>7.6</v>
+        <v>8.01</v>
       </c>
       <c r="M46" t="n">
         <v>4.07</v>
       </c>
       <c r="N46" t="n">
-        <v>3.49</v>
+        <v>3.72</v>
       </c>
       <c r="O46" t="n">
         <v>3.37</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.78</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46121.55208333334</v>
+        <v>46122.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2893.4</v>
+        <v>2955</v>
       </c>
       <c r="I47" t="n">
         <v>2928.827010802208</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K47" t="n">
-        <v>4.84</v>
+        <v>2.82</v>
       </c>
       <c r="L47" t="n">
         <v>4.17</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>7.71</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46161.55208333334</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>3120.4</v>
+        <v>2914.7</v>
       </c>
       <c r="I48" t="n">
         <v>2969.097862657138</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K48" t="n">
-        <v>5.6</v>
+        <v>-1.36</v>
       </c>
       <c r="L48" t="n">
         <v>3.55</v>
       </c>
       <c r="M48" t="n">
-        <v>1.22</v>
+        <v>5.46</v>
       </c>
       <c r="N48" t="n">
-        <v>3.69</v>
+        <v>7.38</v>
       </c>
       <c r="O48" t="n">
         <v>1.82</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46181.55208333334</v>
+        <v>46182.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2685.2</v>
+        <v>2845</v>
       </c>
       <c r="I49" t="n">
         <v>2839.682928387988</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>7.87</v>
+        <v>2.39</v>
       </c>
       <c r="L49" t="n">
         <v>1.21</v>
@@ -3234,7 +3821,7 @@
         <v>0.52</v>
       </c>
       <c r="N49" t="n">
-        <v>2.35</v>
+        <v>6.84</v>
       </c>
       <c r="O49" t="n">
         <v>-7.38</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46198.38541666666</v>
+        <v>46198.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>2719.7</v>
+        <v>2679.9</v>
       </c>
       <c r="I50" t="n">
         <v>2718.195990114671</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.4</v>
+        <v>-5.8</v>
       </c>
       <c r="L50" t="n">
-        <v>5.36</v>
+        <v>6.15</v>
       </c>
       <c r="M50" t="n">
         <v>0.57</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.76</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46220.55208333334</v>
+        <v>46223.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>2620</v>
+        <v>2656.5</v>
       </c>
       <c r="I51" t="n">
         <v>2640.470667444277</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>2.24</v>
+        <v>0.87</v>
       </c>
       <c r="L51" t="n">
         <v>1.66</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>3.89</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>2719</v>
+        <v>2513.3</v>
       </c>
       <c r="I52" t="n">
         <v>2693.954008830548</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K52" t="n">
-        <v>2.35</v>
+        <v>-5.39</v>
       </c>
       <c r="L52" t="n">
-        <v>1.07</v>
+        <v>5.44</v>
       </c>
       <c r="M52" t="n">
         <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>1.46</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="O52" t="n">
         <v>1.6</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.59</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46268.55208333334</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>2410</v>
+        <v>2472.9</v>
       </c>
       <c r="I53" t="n">
         <v>2465.68451703538</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>4.11</v>
+        <v>1.61</v>
       </c>
       <c r="L53" t="n">
         <v>7.45</v>
@@ -3462,7 +4097,7 @@
         <v>0.87</v>
       </c>
       <c r="N53" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="O53" t="n">
         <v>-8.789999999999999</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>4.98</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46274.55208333334</v>
+        <v>46275.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>2385</v>
+        <v>2359.9</v>
       </c>
       <c r="I54" t="n">
         <v>2368.217012035778</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.55</v>
+        <v>-4.57</v>
       </c>
       <c r="L54" t="n">
-        <v>4.26</v>
+        <v>4.72</v>
       </c>
       <c r="M54" t="n">
         <v>0.85</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.76</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46286.55208333334</v>
+        <v>46287.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2326.5</v>
+        <v>2401.8</v>
       </c>
       <c r="I55" t="n">
         <v>2379.385848662467</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K55" t="n">
-        <v>1.42</v>
+        <v>-1.78</v>
       </c>
       <c r="L55" t="n">
-        <v>1.6</v>
+        <v>2.92</v>
       </c>
       <c r="M55" t="n">
-        <v>0.35</v>
+        <v>1.65</v>
       </c>
       <c r="N55" t="n">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="O55" t="n">
         <v>-1.34</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.77</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2287.3</v>
+        <v>2237.1</v>
       </c>
       <c r="I56" t="n">
         <v>2280.601002982785</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.77</v>
+        <v>-6.86</v>
       </c>
       <c r="L56" t="n">
-        <v>5.49</v>
+        <v>7.34</v>
       </c>
       <c r="M56" t="n">
         <v>0.96</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3693,6 +4376,14 @@
       <c r="Q57" t="n">
         <v>36</v>
       </c>
+      <c r="R57" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5795,7 +6486,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="6">
@@ -5805,7 +6496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -5815,7 +6506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="8">
@@ -5825,7 +6516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5835,7 +6526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39.1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -5845,7 +6536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75.7</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -5855,7 +6546,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -5865,7 +6556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -5875,7 +6566,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.3</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="14">
@@ -5885,7 +6576,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.52</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="15">
@@ -5895,7 +6586,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.27</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="16">
@@ -5905,7 +6596,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.78</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="17">
@@ -5915,7 +6606,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.7</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="18">
@@ -5925,7 +6616,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.2</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="19">
@@ -5935,7 +6626,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.57</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="20">
@@ -5945,7 +6636,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="21">
@@ -5955,7 +6646,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.76</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="22">
@@ -5965,7 +6656,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -5975,7 +6666,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -5985,7 +6676,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="25">
@@ -5995,7 +6686,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.07</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -6005,7 +6696,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.7</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="27">
@@ -6015,7 +6706,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.18</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="28">
@@ -6025,7 +6716,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
